--- a/data/Inventaire.xlsx
+++ b/data/Inventaire.xlsx
@@ -977,17 +977,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -1004,17 +1004,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E3" s="7" t="n">
         <v>46171</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>230</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5">
@@ -1058,20 +1058,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="H5" t="n">
-        <v>250</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -1088,17 +1088,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="G6" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>290</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E7" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -3781,7 +3781,7 @@
         <v>46752</v>
       </c>
       <c r="H3" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3808,7 +3808,7 @@
         <v>46387</v>
       </c>
       <c r="I4" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3835,10 +3835,10 @@
         <v>46387</v>
       </c>
       <c r="H5" t="n">
-        <v>220</v>
+        <v>65</v>
       </c>
       <c r="J5" t="n">
-        <v>250</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
